--- a/dist/materials.xlsx
+++ b/dist/materials.xlsx
@@ -17,7 +17,6 @@
     <sheet name="生物可降解高分子" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="功能高分子" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="基础术语与使用说明" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="重点回收文献" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2585,492 +2584,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="66" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="61" customWidth="1" min="4" max="4"/>
-    <col width="66" customWidth="1" min="5" max="5"/>
-    <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="76" customWidth="1" min="7" max="7"/>
-    <col width="49" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>材料</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>题名/资料</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>年份或公开日</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>技术路线/可学习内容</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>已核查结论与范围</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>现有技术边界/设计关注点</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>来源链接</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>访问与数据口径</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>PTT</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Efficient Depolymerization and Recycling of Poly(trimethylene terephthalate) Using 1,3-Propanediol as Reaction Media</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1,3-PDO同源醇解，Zn(OAc)₂催化，回BHPT并再聚合</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>220℃、0.2 wt%催化剂、PDO/PTT=8:1，45 min，BHPT 83 mol%；比例的具体基准应核对原文</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>同源PDO与醋酸锌组合已公开；印迹与空间位点应建立独立贡献</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s10924-025-03580-x</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>出版社摘要/题录及公开索引；不代表已取得全部补充数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>PET/PBT/PTT</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Sustainable Recycling of Polyester Wastes Using a Coordinatively Unsaturated Zn Catalyst</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>缺陷ZnO在空气与水中催化水解，获得TPA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>PBT/PTT：190℃、6 h，TPA收率&gt;99%；以PET进行40 g放大与5轮回用；浸出结论需结合检测限</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>缺陷Zn羰基活化已有实证；TPA水解路线不同于BHPT醇解</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1038/s41467-026-71862-6</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>开放论文PDF已核查；循环/放大不能直接当PTT结果</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>PTT</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Catalyst-Free Ammonolysis of PTT Polyester: Thermodynamics, Kinetics, and Selective Recovery of 1,3-Propanediol</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>无催化剂氨解，萃取—精馏回收PDO，建立相平衡和动力学模型</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>摘要确认未解离NH₃为反应物种，并讨论缩核与均相并行；具体纯度和回收率未补填</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PDO回收并非空白；可关注低氨耗、分離与母液再生</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/aic.70298</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>已核查出版社摘要；全文/详细收率未核实</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PTT</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CN116969829A：一种化学回收1,3-丙二醇和联产芳香类化学品的工艺方法</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2023-10-31</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>PTT氨解、过滤、酸化、萃取、减压蒸馏，联产酰胺/TPA/PDO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>25%～28%氨水、40～180℃、3～36 h为公开范围；公开文本PDO粗产品纯度约75%～90%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>PTT氨解—PDO萃取精馏组合需查重；授权与法律状态需在官方数据库复核</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://patents.google.com/patent/CN116969829A/zh</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>公开A文本已核查；不同数据库状态可能不同</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>PET（邻近PTT）</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Recyclable Zinc Cyanamide Dual-Site Catalyst Enables Efficient PET Glycolysis</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ZnNCN酸性位点与EG氢键协同活化</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>出版社摘要：PET转化100%，BHET收率92.3%；未写未核查循环条件</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>酸位点＋氢键双活化属于现有技术；不能只以双位点概念建立创造性</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1021/acsapm.4c03337</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>已核查出版社摘要索引，正文访问受限</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>PET（邻近PTT）</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Catalytic Depolymerization of Polyester Waste via Zinc Oxide-Decorated Silica</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2025在线/2026卷期</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SiO₂支撑缺陷ZnO催化EG醇解制BHET</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>摘要：BHET收率92.5%、纯度99%，5轮后约90%；不要把生命周期数字直接写成实验能耗</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SiO₂负载锌与缺陷活化已有完整方案；需区别模板孔穴和位点定位</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/advs.202514922</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>已核查出版社摘要，具体测试条件需全文核对</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PET（邻近PTT）</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Sustainable Plastic Bottle Recycling: Employing Zinc-Deposited SBA-15 as a Catalyst for Glycolysis of PET</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2024-03-06</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SBA-15浸渍不同锌盐，比较酸量和EG醇解</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PET:EG=1:5、催化剂1%、200℃、2 h，ZnCl₂/SBA-15 BHET 75%；循环3次</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>普通Zn/SBA-15为直接材料结构对照；不能泛称SBA-15负载锌首次用于醇解</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3934/environsci.2024006</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>开放出版社资料已核查；比例仍应核对质量基准</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>PTT环状二聚体</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>US6576774B2：Process for Recycling Polytrimethylene Terephthalate Cyclic Dimer</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2003-06-10</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PDO中碱催化开环线性化，再回PTT聚合；可过滤或中和</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>125℃约1 h为部分实施例；公开了K₂CO₃等碱；当前显示失效</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>环状二聚体开环与回用已是先例；作表面印迹模板需另建贡献</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://patents.google.com/patent/US6576774B2/en</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>公开专利全文已核查；法律状态仅数据库显示</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PPE</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CN115869871B：一种不饱和基团封端的低分子量双端基聚苯醚的连续化生产的方法</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>微通道单体氧化偶联、酸酐封端、分段pH调节与萃取</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>主发明从酚单体合成低分子PPE；背景列明高分子PPO再分配路线</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>不得把单体氧化聚合误写废PPE解聚；需区分26DMBQ目标</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://patents.google.com/patent/CN115869871B/zh</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>公开专利全文已核查；现行权利要求需正式比对</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>废TPEE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CN116065261：热塑性聚酯弹性体复合纤维及其制造方法以及织物</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2023公开/2024授权</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>废TPEE化学醇解与物理回收料配混制复合纤维</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>公开涉及PBT型/ PET型TPEE醇解；重点为再生料配混和芯鞘纤维</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>废TPEE醇解非空白；聚焦完整PTMEG回收、纯化和再聚合</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://patents.google.com/patent/CN116065261A/zh</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>前序整理资料；本表保留查重线索，未重新逐项核验B文本</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dist/materials.xlsx
+++ b/dist/materials.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -449,6 +449,11 @@
     <col width="52" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="72" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -522,6 +527,31 @@
           <t>参考来源与核验范围</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃化转变温度(℃)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>熔点(℃)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>热变形温度(℃)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>密度(g/cm³)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>加工温度(℃)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -594,6 +624,23 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O2" t="n">
+        <v>-120</v>
+      </c>
+      <c r="P2" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>45</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>160 ~ 240</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -666,6 +713,23 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>100</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>180 ~ 240</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -738,6 +802,20 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O4" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>70</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>160 ~ 200</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -810,6 +888,20 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>85</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>180 ~ 250</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -882,6 +974,20 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://www.ensingerplastics.com/en-sg/thermoplastic-materials/abs-plastic</t>
         </is>
       </c>
+      <c r="O6" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>90</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>200 ~ 250</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -954,6 +1060,20 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O7" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>95</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>200 ~ 250</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1026,6 +1146,20 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O8" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>95</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>200 ~ 260</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1098,6 +1232,20 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O9" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>95</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>220 ~ 260</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1170,6 +1318,20 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O10" t="n">
+        <v>-30</v>
+      </c>
+      <c r="P10" t="n">
+        <v>85</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>130 ~ 190</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1242,6 +1404,17 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://www.kuraray-poval.com/fileadmin/technical_information/brochures/poval/KURARAY_POVAL_application_guide.pdf</t>
         </is>
       </c>
+      <c r="O11" t="n">
+        <v>85</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>180 ~ 220</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1314,6 +1487,20 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>175</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>150 ~ 200</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1385,6 +1572,12 @@
         <is>
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
+      </c>
+      <c r="O13" t="n">
+        <v>30</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>
@@ -2590,7 +2783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2607,6 +2800,11 @@
     <col width="52" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="72" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -2680,6 +2878,31 @@
           <t>参考来源与核验范围</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃化转变温度(℃)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>熔点(℃)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>热变形温度(℃)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>密度(g/cm³)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>加工温度(℃)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2752,6 +2975,23 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://www.ensingerplastics.com/en-sg/thermoplastic-materials/pa-polyamide</t>
         </is>
       </c>
+      <c r="O2" t="n">
+        <v>50</v>
+      </c>
+      <c r="P2" t="n">
+        <v>220</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>75</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>230 ~ 280</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2824,6 +3064,23 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://www.ensingerplastics.com/en-sg/thermoplastic-materials/pa-polyamide</t>
         </is>
       </c>
+      <c r="O3" t="n">
+        <v>70</v>
+      </c>
+      <c r="P3" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>90</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>260 ~ 300</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2896,6 +3153,20 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://www.ensingerplastics.com/en-sg/thermoplastic-materials/pc-polycarbonate</t>
         </is>
       </c>
+      <c r="O4" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>135</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>260 ~ 320</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2968,6 +3239,23 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O5" t="n">
+        <v>-60</v>
+      </c>
+      <c r="P5" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>110</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>190 ~ 210</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3040,6 +3328,20 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://www.ensingerplastics.com/en-sg/thermoplastic-materials/ppe-plastic</t>
         </is>
       </c>
+      <c r="O6" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>120</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>260 ~ 300</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3112,6 +3414,23 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://plastics-rubber.basf.com/asiapacific/en/performance_polymers/products/ultradur</t>
         </is>
       </c>
+      <c r="O7" t="n">
+        <v>45</v>
+      </c>
+      <c r="P7" t="n">
+        <v>225</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>150</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>230 ~ 260</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3184,6 +3503,23 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://www.ensingerplastics.com/en/thermoplastic-materials/pet-polyester</t>
         </is>
       </c>
+      <c r="O8" t="n">
+        <v>78</v>
+      </c>
+      <c r="P8" t="n">
+        <v>255</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>70</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>270 ~ 290</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3256,6 +3592,23 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://doi.org/10.1007/s10924-025-03580-x</t>
         </is>
       </c>
+      <c r="O9" t="n">
+        <v>45</v>
+      </c>
+      <c r="P9" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>75</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>240 ~ 270</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3328,6 +3681,23 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O10" t="n">
+        <v>45</v>
+      </c>
+      <c r="P10" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>55</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>200 ~ 250</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3400,6 +3770,23 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O11" t="n">
+        <v>40</v>
+      </c>
+      <c r="P11" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>55</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>200 ~ 260</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3472,6 +3859,20 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O12" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>70</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>230 ~ 260</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3544,6 +3945,20 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O13" t="n">
+        <v>60</v>
+      </c>
+      <c r="P13" t="n">
+        <v>185</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>200 ~ 230</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3614,6 +4029,20 @@
       <c r="N14" t="inlineStr">
         <is>
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>88</v>
+      </c>
+      <c r="P14" t="n">
+        <v>220</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>240 ~ 260</t>
         </is>
       </c>
     </row>
@@ -3628,7 +4057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3645,6 +4074,11 @@
     <col width="52" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="72" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -3718,6 +4152,31 @@
           <t>参考来源与核验范围</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃化转变温度(℃)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>熔点(℃)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>热变形温度(℃)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>密度(g/cm³)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>加工温度(℃)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3790,6 +4249,23 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://www.ensingerplastics.com/en-sg/thermoplastic-materials/pps-plastic</t>
         </is>
       </c>
+      <c r="O2" t="n">
+        <v>90</v>
+      </c>
+      <c r="P2" t="n">
+        <v>285</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>135</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>300 ~ 340</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3862,6 +4338,23 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O3" t="n">
+        <v>143</v>
+      </c>
+      <c r="P3" t="n">
+        <v>343</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>315</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>350 ~ 400</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3934,6 +4427,12 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O4" t="n">
+        <v>400</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.42</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4006,6 +4505,20 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://www.ensingerplastics.com/en-sg/thermoplastic-materials/pei-plastic</t>
         </is>
       </c>
+      <c r="O5" t="n">
+        <v>217</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>200</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>340 ~ 400</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4078,6 +4591,20 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O6" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>175</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>300 ~ 360</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4150,6 +4677,20 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://www.ensingerplastics.com/en-sg/thermoplastic-materials/pes-plastic</t>
         </is>
       </c>
+      <c r="O7" t="n">
+        <v>225</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>205</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>330 ~ 390</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4222,6 +4763,23 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O8" t="n">
+        <v>120</v>
+      </c>
+      <c r="P8" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>240</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>280 ~ 320</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4294,6 +4852,20 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O9" t="n">
+        <v>220</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>205</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>330 ~ 390</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4366,6 +4938,20 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O10" t="n">
+        <v>275</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>260</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>320 ~ 350</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4438,6 +5024,23 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O11" t="n">
+        <v>120</v>
+      </c>
+      <c r="P11" t="n">
+        <v>310</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>170</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>300 ~ 340</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4510,6 +5113,23 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O12" t="n">
+        <v>-110</v>
+      </c>
+      <c r="P12" t="n">
+        <v>327</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>120</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>360 ~ 380</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4582,6 +5202,23 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="O13" t="n">
+        <v>-40</v>
+      </c>
+      <c r="P13" t="n">
+        <v>170</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>110</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>200 ~ 260</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4654,6 +5291,20 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="P14" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>70</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>330 ~ 380</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4726,6 +5377,20 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="P15" t="n">
+        <v>305</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>90</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>350 ~ 400</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4798,6 +5463,20 @@
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
         </is>
       </c>
+      <c r="P16" t="n">
+        <v>265</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>100</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>300 ~ 340</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4868,6 +5547,23 @@
       <c r="N17" t="inlineStr">
         <is>
           <t>基础概览；分类/选材参考Ensinger手册，具体牌号待核验：https://www.ensingerplastics.com/en-us/-/media/ensinger/files/document-teaser-files/brochures/shapes/engineering-plastics-manual-english.ashx</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>160</v>
+      </c>
+      <c r="P17" t="n">
+        <v>340</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>260</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>340 ~ 380</t>
         </is>
       </c>
     </row>
@@ -4882,7 +5578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4899,6 +5595,11 @@
     <col width="52" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="72" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -4972,6 +5673,31 @@
           <t>参考来源与核验范围</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃化转变温度(℃)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>熔点(℃)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>热变形温度(℃)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>密度(g/cm³)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>加工温度(℃)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5044,6 +5770,15 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O2" t="n">
+        <v>170</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>170</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5116,6 +5851,15 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O3" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>130</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5188,6 +5932,15 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O4" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>100</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5260,6 +6013,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R5" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5332,6 +6088,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="Q6" t="n">
+        <v>120</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.48</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5404,6 +6166,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="Q7" t="n">
+        <v>140</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.48</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5476,6 +6244,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R8" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5548,6 +6319,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R9" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5620,6 +6394,15 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O10" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>100</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.15</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5692,6 +6475,15 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O11" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>220</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5764,6 +6556,15 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O12" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>230</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5836,6 +6637,15 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O13" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>180</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5907,6 +6717,9 @@
         <is>
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
+      </c>
+      <c r="R14" t="n">
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -5920,7 +6733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5937,6 +6750,11 @@
     <col width="52" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="72" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -6010,6 +6828,31 @@
           <t>参考来源与核验范围</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃化转变温度(℃)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>熔点(℃)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>热变形温度(℃)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>密度(g/cm³)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>加工温度(℃)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6082,6 +6925,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O2" t="n">
+        <v>-70</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.93</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6154,6 +7003,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6226,6 +7081,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O4" t="n">
+        <v>-100</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.92</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6298,6 +7159,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O5" t="n">
+        <v>-45</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.23</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6370,6 +7237,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O6" t="n">
+        <v>-30</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6442,6 +7315,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O7" t="n">
+        <v>-50</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.86</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6514,6 +7393,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O8" t="n">
+        <v>-65</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.92</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6586,6 +7471,12 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://www.wacker.com/h/medias/6709-EN.pdf</t>
         </is>
       </c>
+      <c r="O9" t="n">
+        <v>-125</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.15</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6658,6 +7549,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O10" t="n">
+        <v>-20</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6730,6 +7627,20 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://www.basf.com/dam/jcr%3Ae42483e4-4087-3544-a6a2-f958427c1030/Elastollan_Properties-Chemical-Properties.pdf</t>
         </is>
       </c>
+      <c r="O11" t="n">
+        <v>-40</v>
+      </c>
+      <c r="P11" t="n">
+        <v>190</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>190 ~ 220</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6802,6 +7713,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O12" t="n">
+        <v>-20</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6874,6 +7791,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O13" t="n">
+        <v>-40</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.27</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6946,6 +7869,20 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://www.celanese.com/products/hytrel</t>
         </is>
       </c>
+      <c r="O14" t="n">
+        <v>-50</v>
+      </c>
+      <c r="P14" t="n">
+        <v>200</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>220 ~ 250</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7018,6 +7955,20 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://hpp.arkema.com/en/product-families/pebax-elastomer-family/</t>
         </is>
       </c>
+      <c r="O15" t="n">
+        <v>-60</v>
+      </c>
+      <c r="P15" t="n">
+        <v>170</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>200 ~ 240</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7090,6 +8041,17 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O16" t="n">
+        <v>-90</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>150 ~ 200</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7162,6 +8124,17 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O17" t="n">
+        <v>-60</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>180 ~ 230</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7234,6 +8207,17 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O18" t="n">
+        <v>-60</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>180 ~ 220</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7306,6 +8290,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O19" t="n">
+        <v>-25</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7377,6 +8367,12 @@
         <is>
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
+      </c>
+      <c r="O20" t="n">
+        <v>-60</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.92</v>
       </c>
     </row>
   </sheetData>
@@ -7390,7 +8386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7407,6 +8403,11 @@
     <col width="52" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="72" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -7480,6 +8481,31 @@
           <t>参考来源与核验范围</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃化转变温度(℃)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>熔点(℃)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>热变形温度(℃)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>密度(g/cm³)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>加工温度(℃)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7552,6 +8578,20 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://www.ensingerplastics.com/en/thermoplastic-materials/pet-polyester</t>
         </is>
       </c>
+      <c r="O2" t="n">
+        <v>78</v>
+      </c>
+      <c r="P2" t="n">
+        <v>255</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>280 ~ 290</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7624,6 +8664,20 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O3" t="n">
+        <v>50</v>
+      </c>
+      <c r="P3" t="n">
+        <v>220</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>260 ~ 280</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7696,6 +8750,20 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>165</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>230 ~ 280</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7768,6 +8836,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O5" t="n">
+        <v>95</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7840,6 +8914,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O6" t="n">
+        <v>85</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7912,6 +8992,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O7" t="n">
+        <v>80</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7984,6 +9070,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O8" t="n">
+        <v>345</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.44</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8056,6 +9148,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O9" t="n">
+        <v>275</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.38</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8128,6 +9226,15 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O10" t="n">
+        <v>-120</v>
+      </c>
+      <c r="P10" t="n">
+        <v>135</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8200,6 +9307,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R11" t="n">
+        <v>1.8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8272,6 +9382,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R12" t="n">
+        <v>2.54</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8344,6 +9457,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O13" t="n">
+        <v>-50</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8416,6 +9535,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R14" t="n">
+        <v>1.56</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8487,6 +9609,12 @@
         <is>
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
+      </c>
+      <c r="O15" t="n">
+        <v>380</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>
@@ -8500,7 +9628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8517,6 +9645,11 @@
     <col width="52" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="72" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -8590,6 +9723,31 @@
           <t>参考来源与核验范围</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃化转变温度(℃)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>熔点(℃)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>热变形温度(℃)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>密度(g/cm³)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>加工温度(℃)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8662,6 +9820,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R2" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8734,6 +9895,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R3" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8806,6 +9970,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R4" t="n">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8878,6 +10045,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R5" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8950,6 +10120,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O6" t="n">
+        <v>-70</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.93</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9022,6 +10198,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O7" t="n">
+        <v>150</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9094,6 +10276,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O8" t="n">
+        <v>45</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.07</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9166,6 +10354,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R9" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9238,6 +10429,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9382,6 +10576,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R12" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9453,6 +10650,9 @@
         <is>
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
+      </c>
+      <c r="R13" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -9466,7 +10666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9483,6 +10683,11 @@
     <col width="52" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="72" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -9556,6 +10761,31 @@
           <t>参考来源与核验范围</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃化转变温度(℃)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>熔点(℃)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>热变形温度(℃)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>密度(g/cm³)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>加工温度(℃)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9628,6 +10858,23 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://totalenergies-corbion.com/products/</t>
         </is>
       </c>
+      <c r="O2" t="n">
+        <v>58</v>
+      </c>
+      <c r="P2" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>55</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>170 ~ 230</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9700,6 +10947,20 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O3" t="n">
+        <v>-60</v>
+      </c>
+      <c r="P3" t="n">
+        <v>60</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>70 ~ 120</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9772,6 +11033,20 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O4" t="n">
+        <v>-35</v>
+      </c>
+      <c r="P4" t="n">
+        <v>115</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>140 ~ 190</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9844,6 +11119,20 @@
           <t>已核查官方资料/论文（对应结构或相关路线，不代表全列逐项实测）：https://plastics-rubber.basf.com/southamerica/en/performance_polymers/products/ecoflex</t>
         </is>
       </c>
+      <c r="O5" t="n">
+        <v>-30</v>
+      </c>
+      <c r="P5" t="n">
+        <v>120</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>140 ~ 200</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9916,6 +11205,20 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>175</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>170 ~ 190</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9988,6 +11291,20 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>170</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>160 ~ 180</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10060,6 +11377,20 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O8" t="n">
+        <v>40</v>
+      </c>
+      <c r="P8" t="n">
+        <v>225</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>220 ~ 260</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10132,6 +11463,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10204,6 +11541,14 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>120 ~ 160</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10276,6 +11621,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10348,6 +11696,20 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O12" t="n">
+        <v>-10</v>
+      </c>
+      <c r="P12" t="n">
+        <v>110</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>130 ~ 160</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10418,6 +11780,20 @@
       <c r="N13" t="inlineStr">
         <is>
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>-40</v>
+      </c>
+      <c r="P13" t="n">
+        <v>95</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>130 ~ 180</t>
         </is>
       </c>
     </row>
@@ -10432,7 +11808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10449,6 +11825,11 @@
     <col width="52" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="72" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -10522,6 +11903,31 @@
           <t>参考来源与核验范围</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃化转变温度(℃)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>熔点(℃)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>热变形温度(℃)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>密度(g/cm³)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>加工温度(℃)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10594,6 +12000,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R2" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10666,6 +12075,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R3" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10738,6 +12150,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R4" t="n">
+        <v>1.33</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10810,6 +12225,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R5" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11026,6 +12444,9 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="R8" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11098,6 +12519,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O9" t="n">
+        <v>165</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11314,6 +12741,23 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O12" t="n">
+        <v>120</v>
+      </c>
+      <c r="P12" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>240</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>280 ~ 320</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11530,6 +12974,23 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O15" t="n">
+        <v>-40</v>
+      </c>
+      <c r="P15" t="n">
+        <v>170</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>110</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>200 ~ 260</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11674,6 +13135,15 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O17" t="n">
+        <v>-60</v>
+      </c>
+      <c r="P17" t="n">
+        <v>65</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.12</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11746,6 +13216,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O18" t="n">
+        <v>106</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11818,6 +13294,12 @@
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
       </c>
+      <c r="O19" t="n">
+        <v>170</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11889,6 +13371,12 @@
         <is>
           <t>原表与基础知识归纳；具体配方、牌号及数值未逐项来源核验</t>
         </is>
+      </c>
+      <c r="O20" t="n">
+        <v>-125</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.97</v>
       </c>
     </row>
   </sheetData>
